--- a/data_extactor/batch_10_fa/batch_0060_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0060_fa.xlsx
@@ -503,32 +503,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | نرم‌افزار مرورگر وب | نرم‌افزار پایگاه داده | نرم‌افزار برنامه‌ریزی | Microsoft Outlook | سیستم‌های مدیریت موجودی | نرم‌افزار Microsoft Office | سیستم مدیریت نگهداری و تعمیرات کامپیوتری CMMS</t>
+          <t>Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | نرم‌افزار مرورگر وب | نرم‌افزار پایگاه داده | نرم‌افزار زمان‌بندی | Microsoft Outlook | سیستم‌های مدیریت موجودی | نرم‌افزار Microsoft Office | سیستم مدیریت نگهداری کامپیوتری CMMS</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | سخن گفتن | درک مطلب خواندن | تفکر انتقادی | نظارت | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>مشتری‌مداری و خدمات شخصی | زبان انگلیسی | ریاضیات | قانون و حکومت | ایمنی و امنیت عمومی | کامپیوتر و الکترونیک | فروش و بازاریابی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | ریاضیات | قانون و دولت | ایمنی و امنیت عمومی | رایانه و الکترونیک | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | اشتراک زمانی | چالاکی انگشتان | چالاکی دست | بینایی دور | حفظ کردن | روان بودن ایده‌ها</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تقسیم توجه | مهارت انگشتان | مهارت دستی | بینایی دور | حفظ کردن | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>تماس با دیگران | برخورد با مشتریان خارجی یا عموم مردم به‌طور کلی | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | نزدیکی فیزیکی | صرف زمان به حالت ایستاده | صرف زمان به پیاده‌روی یا دویدن | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | داخل ساختمان، محیط کنترل‌شده | اهمیت تکرار وظایف یکسان | فشار زمانی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | سطح رقابت | قرار گرفتن در معرض صداها، سطوح نویز مزاحم یا ناراحت‌کننده | اهمیت دقیق یا درست بودن | پیامد خطا</t>
+          <t>ارتباط با دیگران | تعامل با مشتریان خارجی یا عموم مردم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | نزدیکی فیزیکی | صرف زمان برای ایستادن | صرف زمان برای راه رفتن یا دویدن | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت تکرار وظایف یکسان | فشار زمانی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | سطح رقابت | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | اهمیت دقیق یا درست بودن | پیامد خطا</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>دیلرهای قمار | نویسندگان و دوندگان ثبت شرط‌بندی قمار و ورزش | کارکنان باجه قمار | تعویض‌کنندگان پول قمار و صندوق‌داران غرفه | سرپرستان خط اول کارکنان خدمات قمار | ماموران نظارت بر قمار و بازرسان قمار | مدیران قمار | متصدیان تفریح و سرگرمی | راهنماها، متصدیان لابی و بلیط‌گیرها | صندوق‌داران | کارمندان پیشخوان و اجاره | نمایندگان خدمات مشتریان | میزبانان و مهمان‌داران، رستوران، سالن و کافی‌شاپ | متصدیان بار | پیشخدمت‌های مرد و زن | نگهبانان امنیتی | دربان‌ها | کارکنان خدمات سرگرمی و مشاغل مرتبط، سایر | مدیران سرگرمی و تفریح، به‌جز قمار | کارکنان تفریحی</t>
+          <t>دیلرهای قمار | نویسندگان و دوندگان دفاتر شرط‌بندی ورزشی و قمار | کارکنان باجه قمارخانه | صندوق‌داران غرفه و مسئولان پول خرد قماربازی | سرپرستان خط اول کارگران خدمات قمار | ماموران نظارت بر قمار و بازرسان قمار | مدیران قماربازی | متصدیان تفریح و سرگرمی | راهنماها، متصدیان لابی و بلیط‌گیرها | صندوق‌داران | کارمندان باجه و اجاره | نمایندگان خدمات مشتریان | میزبانان رستوران، سالن و کافی‌شاپ | بارتندرها | پیشخدمت‌ها و گارسون‌ها | نگهبانان امنیتی | کانسرج‌ها | کارکنان خدمات سرگرمی و مشاغل مرتبط، سایر | مدیران سرگرمی و تفریح، به جز قماربازی | کارکنان تفریحات</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,27 +565,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>سخن گفتن | گوش دادن فعال | درک مطلب خواندن</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>کامپیوتر و الکترونیک | مشتری‌مداری و خدمات شخصی | مکانیک | زبان انگلیسی</t>
+          <t>رایانه و الکترونیک | خدمات مشتری و شخصی | مکانیک | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>بینایی دور | بینایی نزدیک | دقت کنترل | حساسیت به مسئله | بیان شفاهی | درک شفاهی | سرعت ادراکی | ترتیب‌دهی اطلاعات | درک کتبی | تشخیص رنگ بصری | زمان عکس‌العمل | چالاکی انگشتان | چالاکی دست | ثبات دست و بازو | توجه انتخابی | وضوح گفتار | تشخیص گفتار</t>
+          <t>بینایی دور | بینایی نزدیک | دقت کنترل | حساسیت به مسئله | بیان شفاهی | درک شفاهی | سرعت ادراکی | ترتیب‌دهی اطلاعات | درک کتبی | تشخیص رنگ بصری | زمان عکس‌العمل | مهارت انگشتان | مهارت دستی | ثبات دست و بازو | توجه انتخابی | وضوح گفتار | تشخیص گفتار</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>داخل ساختمان، محیط کنترل‌شده | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | آزادی در تصمیم‌گیری | مکالمات تلفنی | فراوانی تصمیم‌گیری | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | ایمیل | تماس با دیگران</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | آزادی در تصمیم‌گیری | مکالمات تلفنی | فراوانی تصمیم‌گیری | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | ایمیل | ارتباط با دیگران</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>تکنسین‌های صدا و تصویر | نصاب‌ها و تعمیرکاران تجهیزات صوتی و تصویری | تکنسین‌های پخش | اپراتورهای دوربین، تلویزیون، ویدیو و فیلم | تعمیرکاران دوربین و تجهیزات عکاسی | سرویس‌کاران و تعمیرکاران ماشین‌های سکه‌ای، فروش خودکار و تفریحی | تعمیرکاران کامپیوتر، خودپرداز و ماشین‌های اداری | نصاب‌ها و تعمیرکاران تجهیزات الکترونیکی، وسایل نقلیه موتوری | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن و شکل‌دهی، الیاف مصنوعی و شیشه | تکنسین‌های نورپردازی | مدیران/کارگردانان فنی رسانه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فرز و صفحه‌تراش، فلز و پلاستیک | اپراتورهای ماشین‌های اداری، به‌جز کامپیوتر | تکنسین‌های آزمایشگاه چشم‌پزشکی | کارکنان فرآیند عکاسی و اپراتورهای ماشین‌های پردازش | تکنسین‌های فوتونیک | تکنسین‌ها و کارکنان پیش از چاپ | نصاب‌ها و تعمیرکاران تجهیزات رادیویی، سلولار و دکل | تکنسین‌های مهندسی صدا | نصاب‌ها و تعمیرکاران تجهیزات مخابراتی، به‌جز نصاب‌های خطوط</t>
+          <t>تکنسین‌های صوتی و تصویری | نصب‌کنندگان و تعمیرکنندگان تجهیزات صوتی و تصویری | تکنسین‌های پخش | اپراتورهای دوربین، تلویزیون، ویدئو و فیلم | تعمیرکاران دوربین و تجهیزات عکاسی | سرویس‌کاران و تعمیرکاران ماشین‌های سکه‌ای، فروش خودکار و تفریحی | تعمیرکاران کامپیوتر، عابربانک و ماشین‌های اداری | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکترونیکی، وسایل نقلیه موتوری | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه | تکنسین‌های نورپردازی | مدیران/کارگردانان فنی رسانه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | اپراتورهای ماشین‌های اداری، به جز رایانه | تکنسین‌های آزمایشگاه چشم‌پزشکی | کارگران فرآیندهای عکاسی و اپراتورهای ماشین‌های فرآوری | تکنسین‌های فوتونیک | تکنسین‌ها و کارگران پیش از چاپ | نصابان و تعمیرکاران تجهیزات رادیویی، سلولی و دکل | تکنسین‌های مهندسی صدا | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز نصابان خطوط</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>مشتری‌مداری و خدمات شخصی | زبان انگلیسی | ایمنی و امنیت عمومی | ارتباطات و رسانه</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | ایمنی و امنیت عمومی | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -637,12 +637,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>تماس با دیگران | داخل ساختمان، محیط کنترل‌شده | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | برخورد با مشتریان خارجی یا عموم مردم به‌طور کلی | نزدیکی فیزیکی | صرف زمان به حالت ایستاده | کار با یا مشارکت در یک گروه کاری یا تیم | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | قرار گرفتن در معرض صداها، سطوح نویز مزاحم یا ناراحت‌کننده | اهمیت دقیق یا درست بودن | تلفن همراه | آزادی در تصمیم‌گیری</t>
+          <t>ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعامل با مشتریان خارجی یا عموم مردم | نزدیکی فیزیکی | صرف زمان برای ایستادن | کار با یا مشارکت در یک گروه کاری یا تیم | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | اهمیت دقیق یا درست بودن | مکالمات تلفنی | آزادی در تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>متصدیان تفریح و سرگرمی | باربران چمدان و پادوهای هتل | صندوق‌داران | دربان‌ها | کارمندان پیشخوان و اجاره | نمایندگان خدمات مشتریان | متصدیان سالن غذاخوری و کافه تریا و دستیاران متصدی بار | سرپرستان خط اول کارکنان سرگرمی و تفریح، به‌جز خدمات قمار | مهمان‌داران هواپیما | میزبانان و مهمان‌داران، رستوران، سالن و کافی‌شاپ | کارمندان پذیرش هتل، متل و اقامتگاه | متصدیان رختکن، اتاق لباس و اتاق پرو | مدیران اقامتی | برنامه‌ریزان جلسات، کنوانسیون‌ها و رویدادها | متصدیان پارکینگ | متصدیان مسافران | مسئولان پذیرش و کارمندان اطلاعات | نمایندگان بلیط رزرواسیون و حمل‌ونقل و کارمندان سفر | راهنمایان تور و همراهان | راهنمایان سفر</t>
+          <t>متصدیان تفریح و سرگرمی | باربران چمدان و پادوهای هتل | صندوق‌داران | کانسرج‌ها | کارمندان باجه و اجاره | نمایندگان خدمات مشتریان | خدمه سالن غذاخوری و سلف‌سرویس و دستیاران بارتندر | سرپرستان خط اول کارگران سرگرمی و تفریح، به جز خدمات قمار | مهمانداران هواپیما | میزبانان رستوران، سالن و کافی‌شاپ | کارمندان پذیرش هتل، متل و اقامتگاه | متصدیان رختکن، اتاق لباس و اتاق پرو | مدیران اقامتی | برنامه‌ریزان جلسات، همایش‌ها و رویدادها | متصدیان پارکینگ | متصدیان مسافران | متصدیان پذیرش و کارمندان اطلاعات | نمایندگان بلیط و رزرواسیون حمل و نقل و کارمندان سفر | راهنمایان تور و همراهان | راهنمایان سفر</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>مشتری‌مداری و خدمات شخصی | زبان انگلیسی | ایمنی و امنیت عمومی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -694,12 +694,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | تماس با دیگران | برخورد با مشتریان خارجی یا عموم مردم به‌طور کلی | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان به حالت ایستاده | نزدیکی فیزیکی | فضای باز، قرار گرفتن در معرض تمام شرایط آب و هوایی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان به پیاده‌روی یا دویدن</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | تعامل با مشتریان خارجی یا عموم مردم | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای ایستادن | نزدیکی فیزیکی | فضای باز، در معرض تمام شرایط آب و هوایی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای راه رفتن یا دویدن</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ورزشکاران و رقابت‌کنندگان ورزشی | باربران چمدان و پادوهای هتل | صندوق‌داران | سرویس‌کاران و تعمیرکاران ماشین‌های سکه‌ای، فروش خودکار و تفریحی | دربان‌ها | کارمندان پیشخوان و اجاره | متصدیان سالن غذاخوری و کافه تریا و دستیاران متصدی بار | دیسپچرها، به‌جز پلیس، آتش‌نشانی و آمبولانس | فروشندگان خانه‌به‌خانه، فروشندگان روزنامه و خیابانی و کارکنان مرتبط | مدیران سرگرمی و تفریح، به‌جز قمار | سرپرستان خط اول کارکنان سرگرمی و تفریح، به‌جز خدمات قمار | سرپرستان خط اول کارکنان خدمات قمار | کارمندان پذیرش هتل، متل و اقامتگاه | کارگران و جابجاکنندگان دستی بار، انبار و مواد | نجات‌غریق‌ها، گشت اسکی و سایر کارکنان خدمات حفاظتی تفریحی | متصدیان رختکن، اتاق لباس و اتاق پرو | متصدیان پارکینگ | متصدیان مسافران | داوران و سایر مقامات ورزشی | راهنماها، متصدیان لابی و بلیط‌گیرها</t>
+          <t>ورزشکاران و رقبای ورزشی | باربران چمدان و پادوهای هتل | صندوق‌داران | سرویس‌کاران و تعمیرکاران ماشین‌های سکه‌ای، فروش خودکار و تفریحی | کانسرج‌ها | کارمندان باجه و اجاره | خدمه سالن غذاخوری و سلف‌سرویس و دستیاران بارتندر | دیسپچرهای غیر از پلیس، آتش‌نشانی و آمبولانس | فروشندگان خانه‌به‌خانه، فروشندگان روزنامه و خیابانی و کارکنان مرتبط | مدیران سرگرمی و تفریح، به جز قماربازی | سرپرستان خط اول کارگران سرگرمی و تفریح، به جز خدمات قمار | سرپرستان خط اول کارگران خدمات قمار | کارمندان پذیرش هتل، متل و اقامتگاه | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | نجات‌غریق‌ها، گشت اسکی و سایر کارکنان خدمات حفاظتی تفریحی | متصدیان رختکن، اتاق لباس و اتاق پرو | متصدیان پارکینگ | متصدیان مسافران | داوران، قضاوت‌کنندگان و سایر مقامات ورزشی | راهنماها، متصدیان لابی و بلیط‌گیرها</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -741,22 +741,22 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>هنرهای زیبا | طراحی | تولید و فرآوری | مشتری‌مداری و خدمات شخصی | زبان انگلیسی | روانشناسی</t>
+          <t>هنرهای زیبا | طراحی | تولید و فرآوری | خدمات مشتری و شخصی | زبان انگلیسی | روان‌شناسی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | روان بودن ایده‌ها | ثبات دست و بازو | توجه انتخابی | استدلال استقرایی | استدلال قیاسی | اصالت | درک کتبی | تشخیص گفتار | چالاکی انگشتان</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | روانی ایده‌ها | ثبات دست و بازو | توجه انتخابی | استدلال استقرایی | استدلال قیاسی | اصالت | درک کتبی | تشخیص گفتار | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | داخل ساختمان، محیط کنترل‌شده | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | تماس با دیگران | فشار زمانی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | نزدیکی فیزیکی | ایمیل | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامدهای کاری و نتایج سایر کارکنان | صرف زمان برای انجام حرکات تکراری | فراوانی تصمیم‌گیری</t>
+          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | فشار زمانی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | نزدیکی فیزیکی | ایمیل | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامدهای کاری و نتایج سایر کارکنان | صرف زمان برای انجام حرکات تکراری | فراوانی تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>طراحان حرکات موزون | طراحان تجاری و صنعتی | هنرمندان صنایع دستی | الگوسازان پارچه و پوشاک | طراحان مد | پرداخت‌کاران مبلمان | آرایشگران، استایلیست‌های مو و متخصصان زیبایی | طراحان داخلی | جواهرسازان و سازندگان مصنوعات فلزی و سنگ‌های قیمتی | کارگران خشکشویی و لباسشویی | چهره‌پردازان، تئاتر و اجرا | طراحان ویترین و چیدمان کالا | کارگران نقاشی، پوشش‌دهی و تزئین | فروشندگان خرده‌فروشی | طراحان صحنه و نمایشگاه | دوزندگان دستی | اپراتورهای چرخ خیاطی | کارگران و تعمیرکاران کفش و چرم | خیاطان، دوزندگان لباس زنانه و خیاطان سفارشی | رویه‌کوبان مبل</t>
+          <t>طراحان رقص | طراحان تجاری و صنعتی | هنرمندان صنایع دستی | الگوسازان پارچه و پوشاک | طراحان مد | پرداخت‌کاران مبلمان | آرایشگران زنانه، استایلیست‌های مو و متخصصان زیبایی | طراحان داخلی | جواهرسازان و کارگران سنگ‌ها و فلزات قیمتی | کارکنان خشک‌شویی و لباس‌شویی | میکاپ آرتیست‌های تئاتر و نمایش | چیدمان‌کنندگان کالا و تزئین‌کنندگان ویترین | کارگران نقاشی، پوشش‌دهی و تزیین | فروشندگان خرده‌فروشی | طراحان صحنه و نمایشگاه | دوزندگان دستی | اپراتورهای چرخ خیاطی | کارگران و تعمیرکاران کفش و چرم | خیاطان، دوزندگان زنانه و دوزندگان سفارشی | روکوبان</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>مشتری‌مداری و خدمات شخصی | زبان انگلیسی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -808,12 +808,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>تماس با دیگران | داخل ساختمان، محیط کنترل‌شده | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | برخورد با مشتریان خارجی یا عموم مردم به‌طور کلی | صرف زمان به حالت ایستاده | صرف زمان برای استفاده از دست‌ها جهت جابجایی, کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | نزدیکی فیزیکی | مکالمات تلفنی</t>
+          <t>ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعامل با مشتریان خارجی یا عموم مردم | صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | نزدیکی فیزیکی | مکالمات تلفنی</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>متصدیان تفریح و سرگرمی | باربران چمدان و پادوهای هتل | دربان‌ها | کارمندان پیشخوان و اجاره | متصدیان سالن غذاخوری و کافه تریا و دستیاران متصدی بار | سرپرستان خط اول کارکنان خانه‌داری و سرایداری | سرپرستان خط اول کارکنان خدمات شخصی | توزیع‌کنندگان غذا، غیررستورانی | مدیران خدمات غذایی | میزبانان و مهمان‌داران، رستوران، سالن و کافی‌شاپ | کارمندان پذیرش هتل، متل و اقامتگاه | سرایداران و تمیزکنندگان، به‌جز خدمتکاران و تمیزکنندگان خانه‌داری | کارگران خشکشویی و لباسشویی | مدیران اقامتی | خدمتکاران و تمیزکنندگان خانه‌داری | متصدیان پارکینگ | متصدیان مسافران | فروشندگان خرده‌فروشی | راهنماها، متصدیان لابی و بلیط‌گیرها | پیشخدمت‌های مرد و زن</t>
+          <t>متصدیان تفریح و سرگرمی | باربران چمدان و پادوهای هتل | کانسرج‌ها | کارمندان باجه و اجاره | خدمه سالن غذاخوری و سلف‌سرویس و دستیاران بارتندر | سرپرستان خط اول کارگران خانه‌داری و سرایداری | سرپرستان خط اول کارگران خدمات شخصی | سروکنندگان غذا، غیررستورانی | مدیران خدمات غذایی | میزبانان رستوران، سالن و کافی‌شاپ | کارمندان پذیرش هتل، متل و اقامتگاه | سرایداران و تمیزکنندگان، به جز خدمتکاران و تمیزکنندگان خانه‌داری | کارکنان خشک‌شویی و لباس‌شویی | مدیران اقامتی | خدمتکاران و تمیزکنندگان خانه‌داری | متصدیان پارکینگ | متصدیان مسافران | فروشندگان خرده‌فروشی | راهنماها، متصدیان لابی و بلیط‌گیرها | پیشخدمت‌ها و گارسون‌ها</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -845,32 +845,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | نرم‌افزار مرورگر وب | نرم‌افزار پایگاه داده | نرم‌افزار برنامه‌ریزی | Microsoft Outlook | سیستم‌های مدیریت موجودی | نرم‌افزار Microsoft Office | سیستم مدیریت نگهداری و تعمیرات کامپیوتری CMMS</t>
+          <t>Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل | نرم‌افزار مرورگر وب | نرم‌افزار پایگاه داده | نرم‌افزار زمان‌بندی | Microsoft Outlook | سیستم‌های مدیریت موجودی | نرم‌افزار Microsoft Office | سیستم مدیریت نگهداری کامپیوتری CMMS</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | سخن گفتن | درک مطلب خواندن | تفکر انتقادی | نظارت | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>مشتری‌مداری و خدمات شخصی | زبان انگلیسی | ایمنی و امنیت عمومی | فروش و بازاریابی | کامپیوتر و الکترونیک | آموزش و پرورش</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | ایمنی و امنیت عمومی | فروش و بازاریابی | رایانه و الکترونیک | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | اشتراک زمانی | چالاکی انگشتان | چالاکی دست | بینایی دور | حفظ کردن | روان بودن ایده‌ها</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تقسیم توجه | مهارت انگشتان | مهارت دستی | بینایی دور | حفظ کردن | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>تماس با دیگران | برخورد با مشتریان خارجی یا عموم مردم به‌طور کلی | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | نزدیکی فیزیکی | صرف زمان به حالت ایستاده | صرف زمان به پیاده‌روی یا دویدن | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | داخل ساختمان، محیط کنترل‌شده | اهمیت تکرار وظایف یکسان | فشار زمانی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری</t>
+          <t>ارتباط با دیگران | تعامل با مشتریان خارجی یا عموم مردم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | نزدیکی فیزیکی | صرف زمان برای ایستادن | صرف زمان برای راه رفتن یا دویدن | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت تکرار وظایف یکسان | فشار زمانی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>متصدیان تفریح و سرگرمی | راهنماها، متصدیان لابی و بلیط‌گیرها | متصدیان لباس | متصدیان رختکن، اتاق لباس و اتاق پرو | آپاراتچی‌های سینما | کارکنان تفریحی | دربان‌ها | راهنمایان تور و همراهان | راهنمایان سفر | باربران چمدان و پادوهای هتل | صندوق‌داران | کارمندان پیشخوان و اجاره | نمایندگان خدمات مشتریان | نگهبانان امنیتی | نجات‌غریق‌ها، گشت اسکی و سایر کارکنان خدمات حفاظتی تفریحی | سرپرستان خط اول کارکنان سرگرمی و تفریح، به‌جز خدمات قمار | مدیران سرگرمی و تفریح، به‌جز قمار | میزبانان و مهمان‌داران، رستوران، سالن و کافی‌شاپ | نمایندگان بلیط رزرواسیون و حمل‌ونقل و کارمندان سفر | کارکنان خدمات قمار، سایر</t>
+          <t>متصدیان تفریح و سرگرمی | راهنماها، متصدیان لابی و بلیط‌گیرها | متصدیان لباس | متصدیان رختکن، اتاق لباس و اتاق پرو | آپاراتچی‌های سینما | کارکنان تفریحات | کانسرج‌ها | راهنمایان تور و همراهان | راهنمایان سفر | باربران چمدان و پادوهای هتل | صندوق‌داران | کارمندان باجه و اجاره | نمایندگان خدمات مشتریان | نگهبانان امنیتی | نجات‌غریق‌ها، گشت اسکی و سایر کارکنان خدمات حفاظتی تفریحی | سرپرستان خط اول کارگران سرگرمی و تفریح، به جز خدمات قمار | مدیران سرگرمی و تفریح، به جز قماربازی | میزبانان رستوران، سالن و کافی‌شاپ | نمایندگان بلیط و رزرواسیون حمل و نقل و کارمندان سفر | کارکنان خدمات قمار، سایر</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>سخن گفتن | گوش دادن فعال | نگارش | تفکر انتقادی | نظارت | یادگیری فعال | درک مطلب خواندن</t>
+          <t>سخن گفتن | گوش دادن فعال | نگارش | تفکر انتقادی | نظارت | یادگیری فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>مشتری‌مداری و خدمات شخصی | شیمی | روانشناسی | زبان انگلیسی | قانون و حکومت | زیست‌شناسی | مدیریت و سازماندهی | اداری | فلسفه و الهیات</t>
+          <t>خدمات مشتری و شخصی | شیمی | روان‌شناسی | زبان انگلیسی | قانون و دولت | زیست‌شناسی | مدیریت و اداره | اداری | فلسفه و الهیات</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | درک شفاهی | حساسیت به مسئله | ثبات دست و بازو | تشخیص گفتار | بیان شفاهی | استدلال قیاسی | ترتیب‌دهی اطلاعات | وضوح گفتار | چالاکی دست | تجسم | استدلال استقرایی | درک کتبی | بیان کتبی | تشخیص رنگ بصری | قدرت تنه | دقت کنترل | چالاکی انگشتان</t>
+          <t>بینایی نزدیک | درک شفاهی | حساسیت به مسئله | ثبات دست و بازو | تشخیص گفتار | بیان شفاهی | استدلال قیاسی | ترتیب‌دهی اطلاعات | وضوح گفتار | مهارت دستی | تجسم | استدلال استقرایی | درک کتبی | بیان کتبی | تشخیص رنگ بصری | قدرت تنه | دقت کنترل | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | داخل ساختمان، محیط کنترل‌شده | فشار زمانی | فراوانی تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | ایمیل | برخورد با مشتریان خارجی یا عموم مردم به‌طور کلی | اهمیت دقیق یا درست بودن | تماس با دیگران | آزادی در تصمیم‌گیری | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | قرار گرفتن در معرض آلاینده‌ها | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض شرایط خطرناک | نزدیکی فیزیکی | نامه‌ها و یادداشت‌های کتبی | کار با یا مشارکت در یک گروه کاری یا تیم | داخل وسیله نقلیه بسته یا کاربری تجهیزات بسته | پیامد خطا | موقعیت‌های درگیری | استفاده از تجهیزات حفاظتی یا ایمنی عمومی مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | سلامت و ایمنی سایر کارکنان | پیامدهای کاری و نتایج سایر کارکنان | فضای باز، قرار گرفتن در معرض تمام شرایط آب و هوایی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت تکرار وظایف یکسان</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | محیط داخلی، دارای کنترل شرایط محیطی | فشار زمانی | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | ایمیل | تعامل با مشتریان خارجی یا عموم مردم | اهمیت دقیق یا درست بودن | ارتباط با دیگران | آزادی در تصمیم‌گیری | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | قرار گرفتن در معرض آلاینده‌ها | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض شرایط خطرناک | نزدیکی فیزیکی | نامه‌ها و یادداشت‌های کتبی | کار با یا مشارکت در یک گروه کاری یا تیم | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | پیامد خطا | موقعیت‌های تعارض | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | سلامت و ایمنی سایر کارکنان | پیامدهای کاری و نتایج سایر کارکنان | فضای باز، در معرض تمام شرایط آب و هوایی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت تکرار وظایف یکسان</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های ویژه | دستیاران متخصص بیهوشی | پزشکان قانونی | اپراتورهای کوره سوزاندن اجساد | تکنسین‌های آندوسکوپی | متصدیان مراسم تشییع جنازه | مدیران خانه تشییع جنازه | دستیاران سلامت در خانه | پرستاران عملی و حرفه‌ای دارای مجوز | مدیران مراسم، برگزارکنندگان و هماهنگ‌کنندگان تشییع جنازه | متخصصان بیهوشی پرستار | دستیاران پرستاری | دستیاران کاردرمانی | فلبوتومیست‌ها | دستیاران فیزیوتراپی | دستیاران فیزیوتراپیست | پرستاران ثبت‌شده | درمانگران تنفسی | دستیاران جراحی | تکنسین‌های جراحی</t>
+          <t>پرستاران مراقبت‌های ویژه | دستیاران متخصص بیهوشی | بازرسان مرگ | اپراتورهای کوره سوزاندن اجساد | تکنسین‌های آندوسکوپی | متصدیان مراسم تشییع جنازه | مدیران خانه‌های تشییع جنازه | کمک‌یاران سلامت در منزل | پرستاران عملی دارای مجوز و پرستاران حرفه‌ای دارای مجوز | مدیران مراسم تشییع، دفن و آرایشگران متوفی | پرستاران بیهوشی | کمک‌پرستاران | دستیاران کاردرمانی | فلبوتومیست‌ها | کمک‌یاران فیزیوتراپی | دستیاران فیزیوتراپی | پرستاران ثبت‌شده | درمانگران تنفسی | دستیاران جراحی | تکنولوژیست‌های جراحی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,27 +964,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب خواندن | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | مشتری‌مداری و خدمات شخصی | مکانیک | زبان انگلیسی | قانون و حکومت | شیمی | مدیریت و سازماندهی</t>
+          <t>ایمنی و امنیت عمومی | خدمات مشتری و شخصی | مکانیک | زبان انگلیسی | قانون و دولت | شیمی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>چالاکی دست | چالاکی انگشتان | ثبات دست و بازو | هماهنگی چند عضو بدن | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری گسترده | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی | درک کتبی | ترتیب‌دهی اطلاعات</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی | درک کتبی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>داخل ساختمان، محیط غیرکنترل‌شده | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض شرایط خطرناک | استفاده از تجهیزات حفاظتی یا ایمنی عمومی مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | صرف زمان به حالت ایستاده | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت دقیق یا درست بودن | پیامد خطا | اهمیت تکرار وظایف یکسان | سلامت و ایمنی سایر کارکنان | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | برخورد با مشتریان خارجی یا عموم مردم به‌طور کلی | تماس با دیگران | مکالمات تلفنی | آزادی در تصمیم‌گیری | قرار گرفتن در معرض صداها، سطوح نویز مزاحم یا ناراحت‌کننده</t>
+          <t>محیط داخلی، بدون کنترل شرایط محیطی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض شرایط خطرناک | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت دقیق یا درست بودن | پیامد خطا | اهمیت تکرار وظایف یکسان | سلامت و ایمنی سایر کارکنان | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعامل با مشتریان خارجی یا عموم مردم | ارتباط با دیگران | مکالمات تلفنی | آزادی در تصمیم‌گیری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>تیمارگران حیوانات | پزشکان قانونی | مومیایی‌کنندگان | اپراتورهای ماشین‌های حفاری و بارگیری و دراگ‌لاین، معدن‌کاری سطحی | طراحان گل | متصدیان مراسم تشییع جنازه | مدیران خانه تشییع جنازه | کارگران حذف مواد خطرناک | دستیاران سلامت در خانه | کارگران خشکشویی و لباسشویی | خدمتکاران و تمیزکنندگان خانه‌داری | تعمیرکاران ماشین‌آلات | آماده‌سازان تجهیزات پزشکی | مدیران مراسم، برگزارکنندگان و هماهنگ‌کنندگان تشییع جنازه | بهیاران | دستیاران مراقبت شخصی | کارگران بازیافت و احیا | تکنسین‌های جراحی | دستیاران دامپزشکی و تیمارگران حیوانات آزمایشگاهی | تکنسین‌ها و تکنولوژیست‌های دامپزشکی</t>
+          <t>مراقبان حیوانات | بازرسان مرگ | مومیایی‌کنندگان | اپراتورهای ماشین‌های حفاری و بارگیری و درگ‌لاین، معدن‌کاری سطحی | طراحان گل | متصدیان مراسم تشییع جنازه | مدیران خانه‌های تشییع جنازه | کارگران حذف مواد خطرناک | کمک‌یاران سلامت در منزل | کارکنان خشک‌شویی و لباس‌شویی | خدمتکاران و تمیزکنندگان خانه‌داری | کارگران تعمیر و نگهداری ماشین‌آلات | آماده‌سازان تجهیزات پزشکی | مدیران مراسم تشییع، دفن و آرایشگران متوفی | بهیاران | کمک‌یاران مراقبت شخصی | کارگران بازیافت و احیا | تکنولوژیست‌های جراحی | دستیاران دامپزشکی و مراقبان حیوانات آزمایشگاهی | تکنولوژیست‌ها و تکنسین‌های دامپزشکی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>نرم‌افزار حسابداری | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Word | iCIMS Talent Cloud software</t>
+          <t>نرم‌افزار حسابداری | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Word | نرم‌افزار iCIMS Talent Cloud</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>مشتری‌مداری و خدمات شخصی | زبان انگلیسی | اداری | حمل‌ونقل</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | اداری | حمل و نقل</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1036,12 +1036,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | تماس با دیگران | اهمیت دقیق یا درست بودن | برخورد با مشتریان خارجی یا عموم مردم به‌طور کلی | داخل ساختمان، محیط کنترل‌شده | مکالمات تلفنی | فشار زمانی | آزادی در تصمیم‌گیری | داخل وسیله نقلیه بسته یا کاربری تجهیزات بسته | فراوانی تصمیم‌گیری</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | اهمیت دقیق یا درست بودن | تعامل با مشتریان خارجی یا عموم مردم | محیط داخلی، دارای کنترل شرایط محیطی | مکالمات تلفنی | فشار زمانی | آزادی در تصمیم‌گیری | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | فراوانی تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>رانندگان و متصدیان آمبولانس، به‌جز تکنسین‌های فوریت‌های پزشکی | باربران چمدان و پادوهای هتل | دربان‌ها | پزشکان قانونی | اپراتورهای کوره سوزاندن اجساد | مومیایی‌کنندگان | سرپرستان خط اول کارکنان خانه‌داری و سرایداری | سرپرستان خط اول کارکنان خدمات شخصی | مدیران خانه تشییع جنازه | دستیاران سلامت در خانه | خدمتکاران و تمیزکنندگان خانه‌داری | مدیران مراسم، برگزارکنندگان و هماهنگ‌کنندگان تشییع جنازه | دستیاران پرستاری | بهیاران | متصدیان مسافران | دستیاران مراقبت شخصی | مسئولان پذیرش و کارمندان اطلاعات | منشی‌ها و دستیاران اداری، به‌جز حقوقی، پزشکی و اجرایی | انبارداران و پرکنندگان سفارش | راهنماها, متصدیان لابی و بلیط‌گیرها</t>
+          <t>رانندگان و متصدیان آمبولانس، به جز تکنسین‌های فوریت‌های پزشکی | باربران چمدان و پادوهای هتل | کانسرج‌ها | بازرسان مرگ | اپراتورهای کوره سوزاندن اجساد | مومیایی‌کنندگان | سرپرستان خط اول کارگران خانه‌داری و سرایداری | سرپرستان خط اول کارگران خدمات شخصی | مدیران خانه‌های تشییع جنازه | کمک‌یاران سلامت در منزل | خدمتکاران و تمیزکنندگان خانه‌داری | مدیران مراسم تشییع، دفن و آرایشگران متوفی | کمک‌پرستاران | بهیاران | متصدیان مسافران | کمک‌یاران مراقبت شخصی | متصدیان پذیرش و کارمندان اطلاعات | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی | قفسه‌چین‌ها و پرکننده‌های سفارش | راهنماها، متصدیان لابی و بلیط‌گیرها</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0060_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0060_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | ریاضیات | حقوق و مقررات دولتی | ایمنی و امنیت عمومی | رایانه و الکترونیک | فروش و بازاریابی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | ریاضیات | قانون و دولت | ایمنی و امنیت عمومی | رایانه و الکترونیک | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | دید نزدیک | حساسیت به مسئله | مرتب‌سازی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری طبقه‌بندی | تقسیم توجه | چابکی انگشتان | چابکی دستی | دید دور | به‌خاطرسپاری | روانی ایده‌ها</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تقسیم توجه | مهارت انگشتان | مهارت دستی | بینایی دور | حفظ کردن | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>کارت‌پخش‌کن‌های بازی | ثبت‌کنندگان و دوندگان شرط‌بندی ورزشی و بازی‌ها | کارکنان صندوق و باجه بازی | متصدیان تبدیل ژتون و صندوق‌داران باجه | سرپرستان رده‌اول کارکنان خدمات بازی | ماموران نظارت و بازرسان بازی | مدیران سالن‌های بازی | متصدیان اماکن تفریحی و شهربازی | راهنماها، متصدیان سالن انتظار و بلیط‌گیرها | صندوق‌داران | متصدیان باجه و کرایه کالا | کارشناسان خدمات مشتریان | مهمانداران رستوران، سالن و کافی‌شاپ | متصدیان بار | پیشخدمت‌ها | نگهبانان | راهنماهای هتل | سایر متصدیان خدمات سرگرمی و تفریحی | مدیران اماکن تفریحی و سرگرمی، به جز قمار | مربیان و کارشناسان امور تفریحی و اوقات فراغت</t>
+          <t>گردانندگان بازی‌های میزی و کازینویی | متصدیان ثبت و پرداخت شرط‌بندی‌های ورزشی و سرگرمی | متصدیان باجه و خزانه‌داری مراکز بازی و سرگرمی | صندوق‌داران و متصدیان تبدیل ژتون و وجه در مراکز تفریحی | سرپرستان رده‌اول کارکنان خدمات مراکز بازی و سرگرمی | ماموران و بازرسان نظارت تصویری و پایش اماکن سرگرمی و بازی | مدیران سالن‌ها و بازی‌های تفریحی دارای مجوز | متصدیان اماکن تفریحی و شهربازی | راهنماها، متصدیان سالن و بلیط‌گیرها | صندوق‌داران | متصدیان باجه و کرایه کالا و خدمات | کارشناسان خدمات و پشتیبانی مشتریان | میزبانان رستوران، سالن پذیرایی و کافی‌شاپ | متصدیان بار و نوشیدنی | پیش‌خدمتان و گارسون‌ها | نگهبانان و ماموران حراست | متصدیان تشریفات و خدمات میهمانان | سایر متصدیان خدمات سرگرمی و تفریحی | مدیران مجموعه‌های تفریحی، ورزشی و رویدادها | کارکنان و متصدیان امور تفریحی و اوقات فراغت</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | خدمات مشتریان و خدمات فردی | مکانیک | زبان انگلیسی</t>
+          <t>رایانه و الکترونیک | خدمات مشتری و شخصی | مکانیک | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>دید دور | دید نزدیک | دقت در کنترل | حساسیت به مسئله | بیان شفاهی | درک شفاهی | سرعت ادراک | مرتب‌سازی اطلاعات | درک کتبی | تشخیص رنگ | زمان واکنش | چابکی انگشتان | چابکی دستی | پایداری دست و بازو | توجه انتخابی | وضوح گفتار | تشخیص گفتار</t>
+          <t>بینایی دور | بینایی نزدیک | دقت کنترل | حساسیت به مسئله | بیان شفاهی | درک شفاهی | سرعت ادراکی | ترتیب‌دهی اطلاعات | درک کتبی | تشخیص رنگ بصری | زمان عکس‌العمل | مهارت انگشتان | مهارت دستی | ثبات دست و بازو | توجه انتخابی | وضوح گفتار | تشخیص گفتار</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>تکنسین‌های صدا و تصویر | نصابان و تعمیرکاران تجهیزات صوتی و تصویری | تکنسین‌های پخش | تصویربرداران تلویزیون، ویدئو و سینما | تعمیرکاران دوربین و تجهیزات عکاسی | تعمیرکاران و سرویس‌کاران دستگاه‌های سکه‌ای، فروش خودکار و بازی | تعمیرکاران رایانه، خودپرداز و ماشین‌های اداری | نصابان و تعمیرکاران تجهیزات الکترونیکی خودرو | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های شکل‌دهی الیاف | تکنسین‌های نورپردازی | مدیران و کارگردانان فنی رسانه | اپراتورهای ماشین‌های فرز و رنده‌کاری | اپراتورهای ماشین‌های اداری، به‌جز رایانه | تکنسین‌های آزمایشگاه اپتیک و بینایی‌سنجی | کارکنان و اپراتورهای چاپ و پردازش عکس | تکنسین‌های فوتونیک | کارگران و تکنسین‌های پیش از چاپ | نصابان و تعمیرکاران دکل‌ها و تجهیزات رادیویی و سلولار | تکنسین‌های مهندسی صدا | نصابان و تعمیرکاران تجهیزات مخابراتی، به‌جز خطوط ارتباطی</t>
+          <t>تکنسین‌های تجهیزات صوتی و تصویری | نصاب و تعمیرکار تجهیزات صوتی و تصویری | تکنسین‌های پخش و اتاق فرمان | تصویربرداران تلویزیون، ویدیو و سینما | تعمیرکاران دوربین و تجهیزات عکاسی | سرویس‌کاران و تعمیرکاران دستگاه‌های سکه‌ای، فروش خودکار و بازی | تعمیرکاران رایانه، خودپرداز و ماشین‌های اداری | نصاب و تعمیرکار تجهیزات الکترونیکی وسایل نقلیه موتوری | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | تکنسین‌های نورپردازی | مدیران فنی رسانه | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | اپراتورهای ماشین‌آلات اداری، به‌جز رایانه | تکنسین‌های آزمایشگاه و کارگاه ساخت عینک و قطعات اپتیک | کارگران و اپراتورهای ماشین‌های فرآوری و چاپ عکس | تکنسین‌های فوتونیک و اپتیک | تکنسین‌ها و کارگران لیتوگرافی و پیش از چاپ | نصابان و تعمیرکاران تجهیزات رادیویی، سلولار و دکل‌های مخابراتی | تکنسین‌های مهندسی صدا | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز سیم‌بانان</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال</t>
+          <t>سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | ایمنی و امنیت عمومی | ارتباطات و رسانه</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | ایمنی و امنیت عمومی | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>وضوح گفتار | درک شفاهی | بیان شفاهی | دید نزدیک | تشخیص گفتار | حساسیت به مسئله</t>
+          <t>وضوح گفتار | درک شفاهی | بیان شفاهی | بینایی نزدیک | تشخیص گفتار | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>متصدیان اماکن تفریحی و شهربازی | باربرها و باربران هتل | صندوق‌داران | راهنماهای هتل | متصدیان باجه و کرایه کالا | کارشناسان خدمات مشتریان | متصدیان سالن پذیرایی و کمک‌بارتندرها | سرپرستان رده‌اول کارکنان تفریحی و سرگرمی، به‌جز خدمات قمار | مهمانداران هواپیما | مهمانداران رستوران، سالن و کافی‌شاپ | متصدیان پذیرش هتل و مراکز اقامتی | متصدیان رختکن و اتاق پرو | مدیران مراکز اقامتی | برنامه‌ریزان جلسات، همایش‌ها و رویدادها | متصدیان پارکینگ | متصدیان امور مسافران | متصدیان پذیرش و اطلاعات | کارمندان صدور بلیط مسافرتی و آژانس‌های گردشگری | راهنماهای تور و همراهان گردشگری | راهنماهای سفر</t>
+          <t>متصدیان اماکن تفریحی و شهربازی | متصدیان حمل بار و خدمات هتل | صندوق‌داران | متصدیان تشریفات و خدمات میهمانان | متصدیان باجه و کرایه کالا و خدمات | کارشناسان خدمات و پشتیبانی مشتریان | کمک‌پذیرایی‌کنندگان سالن غذاخوری، سلف‌سرویس و کمک‌بارتندرها | سرپرستان رده‌اول کارکنان مراکز تفریحی و سرگرمی، به‌جز بازی‌های شرط‌بندی | مهمانداران هواپیما | میزبانان رستوران، سالن پذیرایی و کافی‌شاپ | متصدیان پذیرش هتل‌ها، متل‌ها و مراکز اقامتی | متصدیان رختکن، امانات و اتاق پرو | مدیران هتل و مراکز اقامتی | کارشناسان برنامه‌ریزی و برگزاری همایش‌ها و رویدادها | متصدیان پارکینگ | مهمانداران و متصدیان خدمات مسافران | متصدیان پذیرش و اطلاعات | متصدیان فروش بلیت، رزرواسیون و خدمات سفر | راهنمایان تور و گردشگری | راهنمایان گردشگری و تور</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال</t>
+          <t>سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | ایمنی و امنیت عمومی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>وضوح گفتار | بیان شفاهی | درک شفاهی | حساسیت به مسئله | تشخیص گفتار | دید نزدیک</t>
+          <t>وضوح گفتار | بیان شفاهی | درک شفاهی | حساسیت به مسئله | تشخیص گفتار | بینایی نزدیک</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ورزشکاران و قهرمانان ورزشی | باربرها و باربران هتل | صندوق‌داران | تعمیرکاران و سرویس‌کاران دستگاه‌های سکه‌ای، فروش خودکار و بازی | راهنماهای هتل | متصدیان باجه و کرایه کالا | متصدیان سالن پذیرایی و کمک‌بارتندرها | متصدیان اعزام و ترابری، به‌جز پلیس، آتش‌نشانی و اورژانس | فروشندگان دوره‌گرد، دکه‌داران و دست‌فروشان خیابانی | مدیران اماکن تفریحی و سرگرمی، به جز قمار | سرپرستان رده‌اول کارکنان تفریحی و سرگرمی، به‌جز خدمات قمار | سرپرستان رده‌اول کارکنان خدمات بازی | متصدیان پذیرش هتل و مراکز اقامتی | کارگران ساده و جابجاکنندگان بار و مواد با دست | نجات‌غریق‌ها، گشت اسکی و سایر کارکنان حفاظتی تفریحی | متصدیان رختکن و اتاق پرو | متصدیان پارکینگ | متصدیان امور مسافران | داوران و مسئولان مسابقات ورزشی | راهنماها، متصدیان سالن انتظار و بلیط‌گیرها</t>
+          <t>ورزشکاران و قهرمانان حرفه‌ای | متصدیان حمل بار و خدمات هتل | صندوق‌داران | سرویس‌کاران و تعمیرکاران دستگاه‌های سکه‌ای، فروش خودکار و بازی | متصدیان تشریفات و خدمات میهمانان | متصدیان باجه و کرایه کالا و خدمات | کمک‌پذیرایی‌کنندگان سالن غذاخوری، سلف‌سرویس و کمک‌بارتندرها | متصدیان دیسپاچ و اعزام | بازاریابان حضوری و فروشندگان خیابانی | مدیران مجموعه‌های تفریحی، ورزشی و رویدادها | سرپرستان رده‌اول کارکنان مراکز تفریحی و سرگرمی، به‌جز بازی‌های شرط‌بندی | سرپرستان رده‌اول کارکنان خدمات مراکز بازی و سرگرمی | متصدیان پذیرش هتل‌ها، متل‌ها و مراکز اقامتی | کارگران جابه‌جایی دستی بار، کالا و مصالح | ناجیان غریق، گشت اسکی و سایر مشاغل خدمات حفاظتی و امدادی تفریحی | متصدیان رختکن، امانات و اتاق پرو | متصدیان پارکینگ | مهمانداران و متصدیان خدمات مسافران | داوران و مسئولان مسابقات ورزشی | راهنماها، متصدیان سالن و بلیط‌گیرها</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | نظارت</t>
+          <t>گوش دادن فعال | سخن گفتن | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>هنرهای تجسمی | طراحی | تولید و پردازش | خدمات مشتریان و خدمات فردی | زبان انگلیسی | روان‌شناسی</t>
+          <t>هنرهای زیبا | طراحی | تولید و فرآوری | خدمات مشتری و شخصی | زبان انگلیسی | روان‌شناسی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | دید نزدیک | وضوح گفتار | انعطاف‌پذیری طبقه‌بندی | مرتب‌سازی اطلاعات | روانی ایده‌ها | پایداری دست و بازو | توجه انتخابی | استدلال استقرایی | استدلال قیاسی | اصالت و ابتکار | درک کتبی | تشخیص گفتار | چابکی انگشتان</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | روانی ایده‌ها | ثبات دست و بازو | توجه انتخابی | استدلال استقرایی | استدلال قیاسی | اصالت | درک کتبی | تشخیص گفتار | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>طراحان حرکات موزون و رقص‌آراها | طراحان تجاری و صنعتی | هنرمندان صنایع دستی | الگوسازان پارچه و پوشاک | طراحان مد و لباس | پرداخت‌کاران مبلمان | آرایشگران و پیرایشگران مو | طراحان دکوراسیون داخلی | جواهرسازان و سازندگان مصنوعات فلزی و سنگی قیمتی | کارکنان خشکشویی و لباسشویی | چهره‌پردازان و گریمورهای تئاتر و سینما | طراحان ویترین و چیدمان کالا | نقاشان، رنگ‌کاران و تزیین‌کاران | فروشندگان خرده‌فروشی | طراحان صحنه و دکور | دوزندگان دستی | چرخکاران و اپراتورهای ماشین دوخت | کارگران و تعمیرکاران کفش و چرم | خیاطان، دوزندگان لباس زنانه و دوزندگان سفارشی | رویه‌کوبان و متصدیان روکش مبلمان</t>
+          <t>طراحان حرکت و کوروگراف‌ها | طراحان تجاری و صنعتی | هنرمندان صنایع دستی | الگوسازان پارچه و پوشاک | طراحان مد و پوشاک | پرداخت‌کاران و رنگ‌کاران چوب و مبلمان | آرایشگران و متخصصان زیبایی | طراحان داخلی | جواهرسازان و سازندگان مصنوعات فلزی و سنگ‌های قیمتی | کارگران خشکشویی و رختشویخانه | چهره‌پردازان و گریموران تئاتر و سینما | طراحان دکوراسیون و ویترین مغازه | کارگران رنگ‌کاری، پوشش‌دهی و تزیین قطعات | فروشندگان خرده‌فروشی | طراحان صحنه و نمایشگاه | دوزندگان دستی | چرخکاران صنعتی | کارگران و تعمیرکاران کفش و چرم | خیاطان و دوزندگان سفارشی | رویه‌کوبان و مبل‌کوبان</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,12 +793,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال</t>
+          <t>سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>متصدیان اماکن تفریحی و شهربازی | باربرها و باربران هتل | راهنماهای هتل | متصدیان باجه و کرایه کالا | متصدیان سالن پذیرایی و کمک‌بارتندرها | سرپرستان رده‌اول کارکنان خانه‌داری و خدمات نظافتی | سرپرستان رده‌اول کارکنان خدمات فردی | مهمانداران پذیرایی غیررستورانی | مدیران خدمات غذا و پذیرایی | مهمانداران رستوران، سالن و کافی‌شاپ | متصدیان پذیرش هتل و مراکز اقامتی | سرایداران و پاکبانان، به‌جز مستخدمان خانه‌داری | کارکنان خشکشویی و لباسشویی | مدیران مراکز اقامتی | خدمتکاران و نظافتچیان خانه‌داری | متصدیان پارکینگ | متصدیان امور مسافران | فروشندگان خرده‌فروشی | راهنماها، متصدیان سالن انتظار و بلیط‌گیرها | پیشخدمت‌ها</t>
+          <t>متصدیان اماکن تفریحی و شهربازی | متصدیان حمل بار و خدمات هتل | متصدیان تشریفات و خدمات میهمانان | متصدیان باجه و کرایه کالا و خدمات | کمک‌پذیرایی‌کنندگان سالن غذاخوری، سلف‌سرویس و کمک‌بارتندرها | سرپرستان رده اول کارگران خدمات و نظافت ساختمان | سرپرستان رده‌اول کارکنان خدمات فردی و مراقبتی | سروکنندگان غذا در محیط‌های غیررستورانی | مدیران خدمات پذیرایی و غذا و نوشیدنی | میزبانان رستوران، سالن پذیرایی و کافی‌شاپ | متصدیان پذیرش هتل‌ها، متل‌ها و مراکز اقامتی | سرایداران و نظافتچیان، به‌جز خدمتکاران و نظافتچیان منازل | کارگران خشکشویی و رختشویخانه | مدیران هتل و مراکز اقامتی | خدمتکاران و نظافتچیان منازل و هتل‌ها | متصدیان پارکینگ | مهمانداران و متصدیان خدمات مسافران | فروشندگان خرده‌فروشی | راهنماها، متصدیان سالن و بلیط‌گیرها | پیش‌خدمتان و گارسون‌ها</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | ایمنی و امنیت عمومی | فروش و بازاریابی | رایانه و الکترونیک | آموزش و پرورش</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | ایمنی و امنیت عمومی | فروش و بازاریابی | رایانه و الکترونیک | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | دید نزدیک | حساسیت به مسئله | مرتب‌سازی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری طبقه‌بندی | تقسیم توجه | چابکی انگشتان | چابکی دستی | دید دور | به‌خاطرسپاری | روانی ایده‌ها</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تقسیم توجه | مهارت انگشتان | مهارت دستی | بینایی دور | حفظ کردن | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>متصدیان اماکن تفریحی و شهربازی | راهنماها، متصدیان سالن انتظار و بلیط‌گیرها | متصدیان و جامه داران لباس صحنه | متصدیان رختکن، امانات و اتاق پرو | آپاراتچی‌ها و تکنسین‌های نمایش فیلم | مربیان و کارشناسان امور تفریحی و اوقات فراغت | راهنماهای هتل | راهنماهای تور و همراهان گردشگری | راهنماهای سفر | باربرها و باربران هتل | صندوق‌داران | متصدیان باجه و کرایه کالا | کارشناسان خدمات مشتریان | نگهبانان | نجات‌غریق‌ها، گشت اسکی و سایر کارکنان حفاظتی تفریحی | سرپرستان رده‌اول کارکنان تفریحی و سرگرمی، به‌جز خدمات قمار | مدیران اماکن تفریحی و سرگرمی، به جز قمار | مهمانداران رستوران، سالن و کافی‌شاپ | کارمندان صدور بلیط مسافرتی و آژانس‌های گردشگری | سایر کارکنان خدمات بازی و سرگرمی</t>
+          <t>متصدیان اماکن تفریحی و شهربازی | راهنماها، متصدیان سالن و بلیط‌گیرها | متصدیان و جامه داران لباس صحنه | متصدیان رختکن، امانات و اتاق پرو | آپاراتچی‌ها و تکنسین‌های نمایش فیلم | کارکنان و متصدیان امور تفریحی و اوقات فراغت | متصدیان تشریفات و خدمات میهمانان | راهنمایان تور و گردشگری | راهنمایان گردشگری و تور | متصدیان حمل بار و خدمات هتل | صندوق‌داران | متصدیان باجه و کرایه کالا و خدمات | کارشناسان خدمات و پشتیبانی مشتریان | نگهبانان و ماموران حراست | ناجیان غریق، گشت اسکی و سایر مشاغل خدمات حفاظتی و امدادی تفریحی | سرپرستان رده‌اول کارکنان مراکز تفریحی و سرگرمی، به‌جز بازی‌های شرط‌بندی | مدیران مجموعه‌های تفریحی، ورزشی و رویدادها | میزبانان رستوران، سالن پذیرایی و کافی‌شاپ | متصدیان فروش بلیت، رزرواسیون و خدمات سفر | سایر کارکنان خدمات بازی و سرگرمی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | نگارش | تفکر انتقادی | نظارت | یادگیری فعال | درک مطلب</t>
+          <t>سخن گفتن | گوش دادن فعال | نگارش | تفکر انتقادی | نظارت | یادگیری فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | شیمی | روان‌شناسی | زبان انگلیسی | حقوق و مقررات دولتی | زیست‌شناسی | مدیریت و امور اداری | امور اداری و دفتری | فلسفه و الهیات</t>
+          <t>خدمات مشتری و شخصی | شیمی | روان‌شناسی | زبان انگلیسی | قانون و دولت | زیست‌شناسی | مدیریت و اداره | اداری | فلسفه و الهیات</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک شفاهی | حساسیت به مسئله | پایداری دست و بازو | تشخیص گفتار | بیان شفاهی | استدلال قیاسی | مرتب‌سازی اطلاعات | وضوح گفتار | چابکی دستی | تجسم فضایی | استدلال استقرایی | درک کتبی | بیان کتبی | تشخیص رنگ | قدرت تنه | دقت در کنترل | چابکی انگشتان</t>
+          <t>بینایی نزدیک | درک شفاهی | حساسیت به مسئله | ثبات دست و بازو | تشخیص گفتار | بیان شفاهی | استدلال قیاسی | ترتیب‌دهی اطلاعات | وضوح گفتار | مهارت دستی | تجسم | استدلال استقرایی | درک کتبی | بیان کتبی | تشخیص رنگ بصری | قدرت تنه | دقت کنترل | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>پرستاران بخش مراقبت‌های ویژه | دستیاران متخصص بیهوشی | پزشکان قانونی | اپراتورهای کوره‌های جسدسوزی | تکنسین‌های اندوسکوپی | متصدیان خدمات مراسم ترحیم | مدیران آرامستان‌ها و سالن‌های ترحیم | مراقبان سلامت در منزل | بهیاران و کمک‌پرستاران دارای مجوز | مدیران تشییع، متصدیان کفن و دفن و برگزارکنندگان مراسم ترحیم | پرستاران متخصص بیهوشی | کمک‌بهیاران | دستیاران کاردرمانی | تکنسین‌های خون‌گیری (فلبوتومیست‌ها) | کمک‌یاران فیزیوتراپی | کاردان‌های فیزیوتراپی | پرستاران رسمی | کارشناسان تنفس‌درمانی | دستیاران جراحی | تکنسین‌های اتاق عمل</t>
+          <t>پرستاران مراقبت‌های حاد | دستیاران متخصص بیهوشی | پزشکان قانونی و بازرسان مرگ مشکوک | اپراتورهای کوره‌های سوزاندن جسد | تکنسین‌های اندوسکوپی | متصدیان و دستیاران خدمات مراسم ترحیم | مدیران آرامستان‌ها و امور خدمات متوفیات | مراقبان سلامت و بهیاران مراقبت در منزل | بهیاران و کمک‌پرستاران دارای مجوز | مدیران و برگزارکنندگان مراسم تشییع و تدفین | پرستاران بیهوشی | کمک‌پرستاران | کاردان‌های کاردرمانی | کارشناسان و تکنسین‌های خون‌گیری | کمک‌یاران فیزیوتراپی | کاردان‌های فیزیوتراپی | پرستاران | کارشناسان مراقبت‌های تنفسی / تنفس‌درمانگران | دستیاران جراحی | تکنسین‌های اتاق عمل</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -959,22 +959,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>نرم‌افزار مدیریت آرامستان Mortware | سامانه HMIS Advantage | Microsoft Excel | Microsoft Word | نرم‌افزار Microsoft Office</t>
+          <t>نرم‌افزار مدیریت آرامستان Mortware | سامانه HMIS Advantage | Microsoft Excel | نرم‌افزار Microsoft Office | نرم‌افزار Microsoft Office</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | خدمات مشتریان و خدمات فردی | مکانیک | زبان انگلیسی | حقوق و مقررات دولتی | شیمی | مدیریت و امور اداری</t>
+          <t>ایمنی و امنیت عمومی | خدمات مشتری و شخصی | مکانیک | زبان انگلیسی | قانون و دولت | شیمی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>چابکی دستی | چابکی انگشتان | پایداری دست و بازو | هماهنگی چند عضو بدن | دقت در کنترل | قدرت ایستا | قدرت تنه | استقامت بدنی | دید نزدیک | دید دور | ادراک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکتی | زمان واکنش | حساسیت به مسئله | درک شفاهی | توجه انتخابی | درک کتبی | مرتب‌سازی اطلاعات</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | قدرت تنه | استقامت | بینایی نزدیک | بینایی دور | درک عمق | هماهنگی کلی بدن | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | زمان عکس‌العمل | حساسیت به مسئله | درک شفاهی | توجه انتخابی | درک کتبی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مراقبان حیوانات | پزشکان قانونی | مومیایی‌کنندگان و فن‌ورزان کالبدآرایی | اپراتورهای ماشین‌آلات حفاری و بارگیری معدن روباز | طراحان گل و گل‌آرایان | متصدیان خدمات مراسم ترحیم | مدیران آرامستان‌ها و سالن‌های ترحیم | کارگران جمع‌آوری و پاکسازی مواد خطرناک | مراقبان سلامت در منزل | کارکنان خشکشویی و لباسشویی | خدمتکاران و نظافتچیان خانه‌داری | تعمیرکاران ماشین‌آلات | تکنسین‌های آماده‌سازی و استریل تجهیزات پزشکی | مدیران تشییع، متصدیان کفن و دفن و برگزارکنندگان مراسم ترحیم | خدمات‌یاران و برانکاردبران بیمارستان | مراقبان خدمات شخصی | کارگران بازیافت و تفکیک مواد | تکنسین‌های اتاق عمل | دستیاران دامپزشکی و مراقبان حیوانات آزمایشگاهی | تکنسین‌ها و کاردان‌های دامپزشکی</t>
+          <t>مراقبان و نگهداران حیوانات | پزشکان قانونی و بازرسان مرگ مشکوک | مومیایی‌کنندگان و فن‌ورزان کالبدآرایی | اپراتورهای ماشین‌آلات حفاری، بارگیری و درگ‌لاین در معادن روباز | طراحان گل و گل‌آراها | متصدیان و دستیاران خدمات مراسم ترحیم | مدیران آرامستان‌ها و امور خدمات متوفیات | کارگران امحا و پاک‌سازی مواد خطرناک | مراقبان سلامت و بهیاران مراقبت در منزل | کارگران خشکشویی و رختشویخانه | خدمتکاران و نظافتچیان منازل و هتل‌ها | کارگران تعمیر و نگهداری ماشین‌آلات | متصدیان آماده‌سازی و استریل تجهیزات پزشکی | مدیران و برگزارکنندگان مراسم تشییع و تدفین | خدمات‌دهندگان و انتقال‌دهندگان بیمار | مراقبان خدمات شخصی و همراهان توان‌خواهان | کارگران بازیافت و تفکیک پسماند | تکنسین‌های اتاق عمل | دستیاران دامپزشکی و متصدیان نگهداری حیوانات آزمایشگاهی | تکنسین‌ها و کارشناسان فناوری دامپزشکی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1016,22 +1016,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>نرم‌افزار حسابداری و دفتری | سامانه‌های مدیریت منابع انسانی iCIMS | Microsoft Excel | Microsoft Word | نرم‌افزار Microsoft Office</t>
+          <t>نرم‌افزار حسابداری | سامانه‌های مدیریت منابع انسانی iCIMS | نرم‌افزار Microsoft Office | Microsoft Word | نرم‌افزار iCIMS Talent Cloud</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>شنیدن فعال | نظارت | سخن گفتن</t>
+          <t>گوش دادن فعال | نظارت | سخن گفتن</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | امور اداری و دفتری | ترابری و حمل‌ونقل</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | اداری | حمل و نقل</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | دید نزدیک | تشخیص گفتار | درک کتبی</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | بینایی نزدیک | تشخیص گفتار | درک کتبی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>رانندگان و متصدیان آمبولانس، به‌جز تکنسین‌های فوریت‌های پزشکی | باربرها و باربران هتل | راهنماهای هتل | پزشکان قانونی | اپراتورهای کوره‌های جسدسوزی | مومیایی‌کنندگان و فن‌ورزان کالبدآرایی | سرپرستان رده‌اول کارکنان خانه‌داری و خدمات نظافتی | سرپرستان رده‌اول کارکنان خدمات فردی | مدیران آرامستان‌ها و سالن‌های ترحیم | مراقبان سلامت در منزل | خدمتکاران و نظافتچیان خانه‌داری | مدیران تشییع، متصدیان کفن و دفن و برگزارکنندگان مراسم ترحیم | کمک‌بهیاران | خدمات‌یاران و برانکاردبران بیمارستان | متصدیان امور مسافران | مراقبان خدمات شخصی | متصدیان پذیرش و اطلاعات | منشی‌ها و مسئولان دفاتر اداری، به‌جز حقوقی، پزشکی و اجرایی | کارگران چیدمان و انبارداری | راهنماها، متصدیان سالن انتظار و بلیط‌گیرها</t>
+          <t>رانندگان و خدمه آمبولانس، به‌جز تکنسین‌های فوریت‌های پزشکی | متصدیان حمل بار و خدمات هتل | متصدیان تشریفات و خدمات میهمانان | پزشکان قانونی و بازرسان مرگ مشکوک | اپراتورهای کوره‌های سوزاندن جسد | مومیایی‌کنندگان و فن‌ورزان کالبدآرایی | سرپرستان رده اول کارگران خدمات و نظافت ساختمان | سرپرستان رده‌اول کارکنان خدمات فردی و مراقبتی | مدیران آرامستان‌ها و امور خدمات متوفیات | مراقبان سلامت و بهیاران مراقبت در منزل | خدمتکاران و نظافتچیان منازل و هتل‌ها | مدیران و برگزارکنندگان مراسم تشییع و تدفین | کمک‌پرستاران | خدمات‌دهندگان و انتقال‌دهندگان بیمار | مهمانداران و متصدیان خدمات مسافران | مراقبان خدمات شخصی و همراهان توان‌خواهان | متصدیان پذیرش و اطلاعات | منشی‌ها و دستیاران اداری عمومی | متصدیان چیدمان و آماده‌سازی سفارش | راهنماها، متصدیان سالن و بلیط‌گیرها</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
